--- a/exports/trend_1d/RECLTD_full_report.xlsx
+++ b/exports/trend_1d/RECLTD_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q87"/>
+  <dimension ref="A1:U87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>10.64</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42118</v>
+        <v>42121</v>
       </c>
       <c r="H2" t="n">
-        <v>120.7</v>
+        <v>117.75</v>
       </c>
       <c r="I2" t="n">
         <v>120.027993503637</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.79</v>
+        <v>-4.19</v>
       </c>
       <c r="L2" t="n">
         <v>6.18</v>
@@ -564,7 +587,19 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>10.49</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42265</v>
+        <v>42268</v>
       </c>
       <c r="H3" t="n">
-        <v>98.45</v>
+        <v>103.05</v>
       </c>
       <c r="I3" t="n">
         <v>99.34528185918234</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="K3" t="n">
-        <v>16.39</v>
+        <v>12.48</v>
       </c>
       <c r="L3" t="n">
         <v>2.85</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>103</v>
+        <v>104</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>6</v>
+      </c>
+      <c r="U3" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>15.42</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42300</v>
+        <v>42303</v>
       </c>
       <c r="H4" t="n">
-        <v>97.45</v>
+        <v>94.5</v>
       </c>
       <c r="I4" t="n">
         <v>94.62333116269771</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K4" t="n">
-        <v>-5.43</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>7.67</v>
+        <v>8.49</v>
       </c>
       <c r="M4" t="n">
         <v>2.08</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42271</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>12.29</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42482</v>
+        <v>42485</v>
       </c>
       <c r="H5" t="n">
-        <v>64.34999999999999</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="I5" t="n">
         <v>64.35928810819385</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="K5" t="n">
-        <v>31.9</v>
+        <v>31.64</v>
       </c>
       <c r="L5" t="n">
         <v>7.46</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>120</v>
+        <v>121</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>7</v>
+      </c>
+      <c r="U5" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>8.92</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42495</v>
+        <v>42496</v>
       </c>
       <c r="H6" t="n">
-        <v>62.95</v>
+        <v>62.1</v>
       </c>
       <c r="I6" t="n">
         <v>62.27994121499262</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.55</v>
+        <v>-3.87</v>
       </c>
       <c r="L6" t="n">
-        <v>3.02</v>
+        <v>4.18</v>
       </c>
       <c r="M6" t="n">
         <v>1.12</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42488</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>10.7</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42541</v>
+        <v>42542</v>
       </c>
       <c r="H7" t="n">
-        <v>62.1</v>
+        <v>63.9</v>
       </c>
       <c r="I7" t="n">
         <v>62.8611992629727</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>-2.9</v>
       </c>
       <c r="L7" t="n">
-        <v>3.38</v>
+        <v>3.78</v>
       </c>
       <c r="M7" t="n">
         <v>2.57</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>7.99</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42676</v>
+        <v>42677</v>
       </c>
       <c r="H8" t="n">
-        <v>95.90000000000001</v>
+        <v>94.15000000000001</v>
       </c>
       <c r="I8" t="n">
         <v>94.63870309448771</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K8" t="n">
-        <v>50.08</v>
+        <v>47.34</v>
       </c>
       <c r="L8" t="n">
         <v>9</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>90</v>
+        <v>91</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>6</v>
+      </c>
+      <c r="U8" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -933,28 +1040,28 @@
         <v>11.69</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42683</v>
+        <v>42684</v>
       </c>
       <c r="H9" t="n">
-        <v>96.59999999999999</v>
+        <v>102.75</v>
       </c>
       <c r="I9" t="n">
         <v>101.9088666971475</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.6</v>
+        <v>-9.130000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>4.3</v>
+        <v>10.36</v>
       </c>
       <c r="M9" t="n">
-        <v>0.86</v>
+        <v>1.71</v>
       </c>
       <c r="N9" t="n">
-        <v>2.71</v>
+        <v>6.37</v>
       </c>
       <c r="O9" t="n">
         <v>-1.82</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,22 +1109,22 @@
         <v>15.01</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42727</v>
+        <v>42730</v>
       </c>
       <c r="H10" t="n">
-        <v>92.05</v>
+        <v>88.05</v>
       </c>
       <c r="I10" t="n">
         <v>90.99725157327373</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K10" t="n">
-        <v>-10.41</v>
+        <v>-14.31</v>
       </c>
       <c r="L10" t="n">
-        <v>11.19</v>
+        <v>14.6</v>
       </c>
       <c r="M10" t="n">
         <v>1.89</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>13.03</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42745</v>
+        <v>42746</v>
       </c>
       <c r="H11" t="n">
-        <v>96.15000000000001</v>
+        <v>100.1</v>
       </c>
       <c r="I11" t="n">
         <v>97.6194916058579</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K11" t="n">
-        <v>-9.199999999999999</v>
+        <v>-13.69</v>
       </c>
       <c r="L11" t="n">
-        <v>11.87</v>
+        <v>14.03</v>
       </c>
       <c r="M11" t="n">
         <v>0.63</v>
       </c>
       <c r="N11" t="n">
-        <v>2.3</v>
+        <v>4.11</v>
       </c>
       <c r="O11" t="n">
         <v>-4.35</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>10.34</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42881</v>
+        <v>42884</v>
       </c>
       <c r="H12" t="n">
-        <v>153.25</v>
+        <v>147.85</v>
       </c>
       <c r="I12" t="n">
         <v>150.6533407379746</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="K12" t="n">
-        <v>53.1</v>
+        <v>47.7</v>
       </c>
       <c r="L12" t="n">
         <v>3.7</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>92</v>
+        <v>93</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>6</v>
+      </c>
+      <c r="U12" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>13.58</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>43033</v>
+        <v>43034</v>
       </c>
       <c r="H13" t="n">
-        <v>122.85</v>
+        <v>125.3</v>
       </c>
       <c r="I13" t="n">
         <v>124.6238005724912</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K13" t="n">
-        <v>16.91</v>
+        <v>15.25</v>
       </c>
       <c r="L13" t="n">
         <v>6.53</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>102</v>
+        <v>103</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42915</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>5</v>
+      </c>
+      <c r="U13" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -1218,25 +1385,25 @@
         <v>9.890000000000001</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>43048</v>
+        <v>43049</v>
       </c>
       <c r="H14" t="n">
-        <v>123.35</v>
+        <v>120.65</v>
       </c>
       <c r="I14" t="n">
         <v>122.9907582081289</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.56</v>
+        <v>-3.71</v>
       </c>
       <c r="L14" t="n">
-        <v>2.59</v>
+        <v>4.19</v>
       </c>
       <c r="M14" t="n">
-        <v>-0</v>
+        <v>0.28</v>
       </c>
       <c r="N14" t="n">
         <v>7.52</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>12.52</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>43087</v>
+        <v>43088</v>
       </c>
       <c r="H15" t="n">
-        <v>113.5</v>
+        <v>117.7</v>
       </c>
       <c r="I15" t="n">
         <v>116.4295595080823</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K15" t="n">
-        <v>5.93</v>
+        <v>2.45</v>
       </c>
       <c r="L15" t="n">
         <v>2.65</v>
       </c>
       <c r="M15" t="n">
-        <v>1.57</v>
+        <v>4.41</v>
       </c>
       <c r="N15" t="n">
-        <v>3.56</v>
+        <v>3.7</v>
       </c>
       <c r="O15" t="n">
         <v>-2.19</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>9.01</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43117</v>
+        <v>43118</v>
       </c>
       <c r="H16" t="n">
-        <v>116.6</v>
+        <v>114.7</v>
       </c>
       <c r="I16" t="n">
         <v>114.7390611505725</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.93</v>
+        <v>-2.55</v>
       </c>
       <c r="L16" t="n">
-        <v>3.57</v>
+        <v>3.78</v>
       </c>
       <c r="M16" t="n">
         <v>0.33</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>8.869999999999999</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43248</v>
+        <v>43249</v>
       </c>
       <c r="H17" t="n">
-        <v>89.5</v>
+        <v>89.7</v>
       </c>
       <c r="I17" t="n">
         <v>89.69757425186438</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K17" t="n">
-        <v>21.97</v>
+        <v>21.8</v>
       </c>
       <c r="L17" t="n">
         <v>5.23</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>5</v>
+      </c>
+      <c r="U17" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>11.59</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43277</v>
+        <v>43278</v>
       </c>
       <c r="H18" t="n">
-        <v>80.65000000000001</v>
+        <v>77.05</v>
       </c>
       <c r="I18" t="n">
         <v>80.46225529201493</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K18" t="n">
-        <v>-10.09</v>
+        <v>-14.1</v>
       </c>
       <c r="L18" t="n">
-        <v>10.54</v>
+        <v>14.72</v>
       </c>
       <c r="M18" t="n">
         <v>1.71</v>
       </c>
       <c r="N18" t="n">
-        <v>4.11</v>
+        <v>4.46</v>
       </c>
       <c r="O18" t="n">
         <v>0.22</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>12.93</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43306</v>
+        <v>43307</v>
       </c>
       <c r="H19" t="n">
-        <v>73.65000000000001</v>
+        <v>80.3</v>
       </c>
       <c r="I19" t="n">
         <v>76.4661365245062</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K19" t="n">
-        <v>4.41</v>
+        <v>-4.22</v>
       </c>
       <c r="L19" t="n">
-        <v>5.19</v>
+        <v>6.1</v>
       </c>
       <c r="M19" t="n">
         <v>1.4</v>
       </c>
       <c r="N19" t="n">
-        <v>6.13</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="O19" t="n">
         <v>-4.46</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>17.1</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43362</v>
+        <v>43364</v>
       </c>
       <c r="H20" t="n">
-        <v>85.2</v>
+        <v>79.84999999999999</v>
       </c>
       <c r="I20" t="n">
         <v>80.27223408522913</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K20" t="n">
-        <v>6.1</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="L20" t="n">
         <v>8.9</v>
@@ -1581,7 +1820,7 @@
         <v>1.6</v>
       </c>
       <c r="N20" t="n">
-        <v>5.66</v>
+        <v>6.28</v>
       </c>
       <c r="O20" t="n">
         <v>9.029999999999999</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>18.47</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43403</v>
+        <v>43404</v>
       </c>
       <c r="H21" t="n">
-        <v>83.65000000000001</v>
+        <v>87.3</v>
       </c>
       <c r="I21" t="n">
         <v>85.6522278285118</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K21" t="n">
-        <v>-4.76</v>
+        <v>-9.33</v>
       </c>
       <c r="L21" t="n">
-        <v>7.76</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="M21" t="n">
         <v>2.16</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,22 +1937,22 @@
         <v>15.57</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43432</v>
+        <v>43433</v>
       </c>
       <c r="H22" t="n">
-        <v>83.15000000000001</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="I22" t="n">
         <v>82.68989102849244</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K22" t="n">
-        <v>-4.75</v>
+        <v>-8.82</v>
       </c>
       <c r="L22" t="n">
-        <v>6.47</v>
+        <v>10.42</v>
       </c>
       <c r="M22" t="n">
         <v>1.38</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>19.77</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43461</v>
+        <v>43462</v>
       </c>
       <c r="H23" t="n">
-        <v>87.15000000000001</v>
+        <v>91.5</v>
       </c>
       <c r="I23" t="n">
         <v>88.76117248406841</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K23" t="n">
-        <v>-9.48</v>
+        <v>-14.95</v>
       </c>
       <c r="L23" t="n">
-        <v>12.25</v>
+        <v>15.89</v>
       </c>
       <c r="M23" t="n">
         <v>1.5</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>14.34</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43500</v>
+        <v>43501</v>
       </c>
       <c r="H24" t="n">
-        <v>91</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="I24" t="n">
         <v>87.88197424198546</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.55</v>
+        <v>-4.26</v>
       </c>
       <c r="L24" t="n">
-        <v>4.32</v>
+        <v>4.7</v>
       </c>
       <c r="M24" t="n">
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
       <c r="N24" t="n">
-        <v>2.99</v>
+        <v>3.74</v>
       </c>
       <c r="O24" t="n">
         <v>4.99</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>12.74</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43517</v>
+        <v>43518</v>
       </c>
       <c r="H25" t="n">
-        <v>96.25</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="I25" t="n">
         <v>98.1399071409722</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K25" t="n">
-        <v>-9.869999999999999</v>
+        <v>-13.98</v>
       </c>
       <c r="L25" t="n">
-        <v>11.59</v>
+        <v>14.55</v>
       </c>
       <c r="M25" t="n">
         <v>0.5600000000000001</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>13.29</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43592</v>
+        <v>43593</v>
       </c>
       <c r="H26" t="n">
-        <v>104.8</v>
+        <v>103.25</v>
       </c>
       <c r="I26" t="n">
         <v>104.6013467918197</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K26" t="n">
-        <v>4.96</v>
+        <v>3.41</v>
       </c>
       <c r="L26" t="n">
         <v>3.51</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>4</v>
+      </c>
+      <c r="U26" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>10.67</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43609</v>
+        <v>43612</v>
       </c>
       <c r="H27" t="n">
-        <v>108.3</v>
+        <v>110.35</v>
       </c>
       <c r="I27" t="n">
         <v>109.8284471150005</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K27" t="n">
-        <v>-4.89</v>
+        <v>-6.88</v>
       </c>
       <c r="L27" t="n">
         <v>8.960000000000001</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>11.38</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43654</v>
+        <v>43655</v>
       </c>
       <c r="H28" t="n">
-        <v>120.35</v>
+        <v>103</v>
       </c>
       <c r="I28" t="n">
         <v>115.5024667672783</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K28" t="n">
-        <v>9.06</v>
+        <v>-6.66</v>
       </c>
       <c r="L28" t="n">
-        <v>5.26</v>
+        <v>8.52</v>
       </c>
       <c r="M28" t="n">
-        <v>0.78</v>
+        <v>5.07</v>
       </c>
       <c r="N28" t="n">
-        <v>3.72</v>
+        <v>14.42</v>
       </c>
       <c r="O28" t="n">
         <v>1.89</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>19.91</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43768</v>
+        <v>43769</v>
       </c>
       <c r="H29" t="n">
-        <v>103.05</v>
+        <v>104.85</v>
       </c>
       <c r="I29" t="n">
         <v>103.0509450579036</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.05</v>
+        <v>-1.8</v>
       </c>
       <c r="L29" t="n">
         <v>13.01</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>4</v>
+      </c>
+      <c r="U29" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>10.31</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43801</v>
+        <v>43802</v>
       </c>
       <c r="H30" t="n">
-        <v>103.45</v>
+        <v>98.05</v>
       </c>
       <c r="I30" t="n">
         <v>98.24219208854404</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K30" t="n">
-        <v>-1.34</v>
+        <v>-6.49</v>
       </c>
       <c r="L30" t="n">
-        <v>4.77</v>
+        <v>6.82</v>
       </c>
       <c r="M30" t="n">
         <v>1.16</v>
       </c>
       <c r="N30" t="n">
-        <v>4.51</v>
+        <v>5.22</v>
       </c>
       <c r="O30" t="n">
         <v>1.75</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43797</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>12.51</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43830</v>
+        <v>43831</v>
       </c>
       <c r="H31" t="n">
-        <v>107.35</v>
+        <v>107.95</v>
       </c>
       <c r="I31" t="n">
         <v>107.6599950981525</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K31" t="n">
-        <v>-9.48</v>
+        <v>-10.1</v>
       </c>
       <c r="L31" t="n">
         <v>10.71</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43825</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,22 +2627,22 @@
         <v>7.58</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43850</v>
+        <v>43851</v>
       </c>
       <c r="H32" t="n">
-        <v>102.9</v>
+        <v>100.8</v>
       </c>
       <c r="I32" t="n">
         <v>101.3240810134402</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K32" t="n">
-        <v>-4.68</v>
+        <v>-6.62</v>
       </c>
       <c r="L32" t="n">
-        <v>5</v>
+        <v>6.86</v>
       </c>
       <c r="M32" t="n">
         <v>1.14</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>9.359999999999999</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43857</v>
+        <v>43858</v>
       </c>
       <c r="H33" t="n">
-        <v>108.1</v>
+        <v>108.7</v>
       </c>
       <c r="I33" t="n">
         <v>108.5670783107399</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K33" t="n">
-        <v>-7.24</v>
+        <v>-7.84</v>
       </c>
       <c r="L33" t="n">
         <v>8.779999999999999</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>9.619999999999999</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>43875</v>
+        <v>43878</v>
       </c>
       <c r="H34" t="n">
-        <v>104.75</v>
+        <v>103.6</v>
       </c>
       <c r="I34" t="n">
         <v>104.4053938585648</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K34" t="n">
-        <v>-3.63</v>
+        <v>-4.69</v>
       </c>
       <c r="L34" t="n">
         <v>6.07</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>11.98</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>43986</v>
+        <v>43987</v>
       </c>
       <c r="H35" t="n">
-        <v>70.15000000000001</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="I35" t="n">
         <v>73.88919133950922</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K35" t="n">
-        <v>32.29</v>
+        <v>27.75</v>
       </c>
       <c r="L35" t="n">
         <v>2.36</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>5</v>
+      </c>
+      <c r="U35" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>16.04</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44095</v>
+        <v>44096</v>
       </c>
       <c r="H36" t="n">
-        <v>76.90000000000001</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="I36" t="n">
         <v>76.64630759579177</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K36" t="n">
-        <v>2.74</v>
+        <v>2.34</v>
       </c>
       <c r="L36" t="n">
         <v>5.74</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>4</v>
+      </c>
+      <c r="U36" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>9.52</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44137</v>
+        <v>44138</v>
       </c>
       <c r="H37" t="n">
-        <v>78.25</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="I37" t="n">
         <v>78.26691961650862</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K37" t="n">
-        <v>-2.15</v>
+        <v>-2.61</v>
       </c>
       <c r="L37" t="n">
-        <v>3.26</v>
+        <v>3.46</v>
       </c>
       <c r="M37" t="n">
         <v>1.12</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>8.98</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44224</v>
+        <v>44225</v>
       </c>
       <c r="H38" t="n">
-        <v>103.65</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="I38" t="n">
         <v>99.71625537199482</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K38" t="n">
-        <v>31.87</v>
+        <v>26.46</v>
       </c>
       <c r="L38" t="n">
         <v>1.84</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>4</v>
+      </c>
+      <c r="U38" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>14.04</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44230</v>
+        <v>44231</v>
       </c>
       <c r="H39" t="n">
-        <v>111.3</v>
+        <v>114.15</v>
       </c>
       <c r="I39" t="n">
         <v>113.3592472780079</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K39" t="n">
-        <v>-11.97</v>
+        <v>-14.84</v>
       </c>
       <c r="L39" t="n">
-        <v>12.88</v>
+        <v>15.39</v>
       </c>
       <c r="M39" t="n">
         <v>1.21</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,22 +3179,22 @@
         <v>13.21</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44250</v>
+        <v>44251</v>
       </c>
       <c r="H40" t="n">
-        <v>104.75</v>
+        <v>103.7</v>
       </c>
       <c r="I40" t="n">
         <v>104.6496244852723</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K40" t="n">
-        <v>-8.23</v>
+        <v>-9.15</v>
       </c>
       <c r="L40" t="n">
-        <v>9.289999999999999</v>
+        <v>13.71</v>
       </c>
       <c r="M40" t="n">
         <v>0.98</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>11.79</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44326</v>
+        <v>44327</v>
       </c>
       <c r="H41" t="n">
-        <v>101.65</v>
+        <v>106.05</v>
       </c>
       <c r="I41" t="n">
         <v>103.0998293064326</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K41" t="n">
-        <v>1.98</v>
+        <v>-2.27</v>
       </c>
       <c r="L41" t="n">
         <v>12.44</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>4</v>
+      </c>
+      <c r="U41" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>10.65</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44364</v>
+        <v>44365</v>
       </c>
       <c r="H42" t="n">
-        <v>112.75</v>
+        <v>110.3</v>
       </c>
       <c r="I42" t="n">
         <v>111.4879880825601</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K42" t="n">
-        <v>6.32</v>
+        <v>4.01</v>
       </c>
       <c r="L42" t="n">
         <v>5.09</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>11.53</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44407</v>
+        <v>44410</v>
       </c>
       <c r="H43" t="n">
-        <v>113.35</v>
+        <v>117.5</v>
       </c>
       <c r="I43" t="n">
         <v>116.6887167636427</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K43" t="n">
-        <v>-2.77</v>
+        <v>-6.53</v>
       </c>
       <c r="L43" t="n">
-        <v>5.26</v>
+        <v>6.89</v>
       </c>
       <c r="M43" t="n">
         <v>0.99</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44371</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>9.73</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44426</v>
+        <v>44428</v>
       </c>
       <c r="H44" t="n">
-        <v>111.05</v>
+        <v>107.95</v>
       </c>
       <c r="I44" t="n">
         <v>108.2937375979389</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K44" t="n">
-        <v>-5.49</v>
+        <v>-8.130000000000001</v>
       </c>
       <c r="L44" t="n">
-        <v>6.98</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="M44" t="n">
         <v>1.37</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>11.18</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44446</v>
+        <v>44447</v>
       </c>
       <c r="H45" t="n">
-        <v>113.15</v>
+        <v>118.15</v>
       </c>
       <c r="I45" t="n">
         <v>117.35720700362</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K45" t="n">
-        <v>-4.82</v>
+        <v>-9.449999999999999</v>
       </c>
       <c r="L45" t="n">
-        <v>8.24</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="M45" t="n">
         <v>0.74</v>
       </c>
       <c r="N45" t="n">
-        <v>2.75</v>
+        <v>4.42</v>
       </c>
       <c r="O45" t="n">
         <v>-2.79</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,22 +3593,22 @@
         <v>9.68</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44490</v>
+        <v>44491</v>
       </c>
       <c r="H46" t="n">
-        <v>115.95</v>
+        <v>113.2</v>
       </c>
       <c r="I46" t="n">
         <v>113.233691437648</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K46" t="n">
-        <v>-1.86</v>
+        <v>-4.19</v>
       </c>
       <c r="L46" t="n">
-        <v>5.04</v>
+        <v>5.21</v>
       </c>
       <c r="M46" t="n">
         <v>1.32</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>12.06</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44568</v>
+        <v>44571</v>
       </c>
       <c r="H47" t="n">
-        <v>102.3</v>
+        <v>105.1</v>
       </c>
       <c r="I47" t="n">
         <v>104.4048413863235</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K47" t="n">
-        <v>9.630000000000001</v>
+        <v>7.16</v>
       </c>
       <c r="L47" t="n">
         <v>5.04</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>4</v>
+      </c>
+      <c r="U47" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>7.33</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44582</v>
+        <v>44585</v>
       </c>
       <c r="H48" t="n">
-        <v>99.7</v>
+        <v>96.95</v>
       </c>
       <c r="I48" t="n">
         <v>98.878811068636</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K48" t="n">
-        <v>-5.14</v>
+        <v>-7.75</v>
       </c>
       <c r="L48" t="n">
-        <v>5.71</v>
+        <v>8.52</v>
       </c>
       <c r="M48" t="n">
         <v>0.24</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>9.220000000000001</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44593</v>
+        <v>44594</v>
       </c>
       <c r="H49" t="n">
-        <v>104.65</v>
+        <v>106.55</v>
       </c>
       <c r="I49" t="n">
         <v>105.273345341873</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K49" t="n">
-        <v>-7.94</v>
+        <v>-9.9</v>
       </c>
       <c r="L49" t="n">
-        <v>8.41</v>
+        <v>10.26</v>
       </c>
       <c r="M49" t="n">
         <v>1.43</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,25 +3869,25 @@
         <v>8.15</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44606</v>
+        <v>44607</v>
       </c>
       <c r="H50" t="n">
-        <v>100.3</v>
+        <v>97.05</v>
       </c>
       <c r="I50" t="n">
         <v>98.29332097816966</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K50" t="n">
-        <v>-5.87</v>
+        <v>-8.92</v>
       </c>
       <c r="L50" t="n">
-        <v>6.29</v>
+        <v>11.45</v>
       </c>
       <c r="M50" t="n">
-        <v>1.06</v>
+        <v>2.94</v>
       </c>
       <c r="N50" t="n">
         <v>3.74</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>8.470000000000001</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44652</v>
+        <v>44655</v>
       </c>
       <c r="H51" t="n">
-        <v>95.15000000000001</v>
+        <v>98.5</v>
       </c>
       <c r="I51" t="n">
         <v>98.1417245711749</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K51" t="n">
-        <v>1.96</v>
+        <v>-1.49</v>
       </c>
       <c r="L51" t="n">
         <v>2.42</v>
@@ -3348,7 +3959,7 @@
         <v>2.11</v>
       </c>
       <c r="N51" t="n">
-        <v>3.09</v>
+        <v>3.52</v>
       </c>
       <c r="O51" t="n">
         <v>-3.24</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>3</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>8.140000000000001</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>44683</v>
+        <v>44685</v>
       </c>
       <c r="H52" t="n">
-        <v>94.90000000000001</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="I52" t="n">
         <v>94.18400357195321</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K52" t="n">
-        <v>-3.65</v>
+        <v>-5.99</v>
       </c>
       <c r="L52" t="n">
-        <v>4.72</v>
+        <v>6.35</v>
       </c>
       <c r="M52" t="n">
         <v>0.84</v>
       </c>
       <c r="N52" t="n">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="O52" t="n">
         <v>3.52</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>8.199999999999999</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>44741</v>
+        <v>44742</v>
       </c>
       <c r="H53" t="n">
-        <v>90</v>
+        <v>92.8</v>
       </c>
       <c r="I53" t="n">
         <v>90.41835810610414</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K53" t="n">
-        <v>2.81</v>
+        <v>-0.22</v>
       </c>
       <c r="L53" t="n">
         <v>3.4</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>7.83</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>44754</v>
+        <v>44755</v>
       </c>
       <c r="H54" t="n">
-        <v>93.09999999999999</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="I54" t="n">
         <v>91.86902641176799</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K54" t="n">
-        <v>0.32</v>
+        <v>-1.29</v>
       </c>
       <c r="L54" t="n">
         <v>2.91</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>8.26</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>44770</v>
+        <v>44771</v>
       </c>
       <c r="H55" t="n">
-        <v>97.15000000000001</v>
+        <v>98.25</v>
       </c>
       <c r="I55" t="n">
         <v>97.21149427123902</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K55" t="n">
-        <v>-6.06</v>
+        <v>-7.26</v>
       </c>
       <c r="L55" t="n">
-        <v>6.77</v>
+        <v>7.7</v>
       </c>
       <c r="M55" t="n">
         <v>0.79</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>5.82</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>44824</v>
+        <v>44825</v>
       </c>
       <c r="H56" t="n">
-        <v>103.55</v>
+        <v>102.85</v>
       </c>
       <c r="I56" t="n">
         <v>102.9795755909259</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K56" t="n">
-        <v>5.39</v>
+        <v>4.68</v>
       </c>
       <c r="L56" t="n">
         <v>0.97</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>6.29</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>44861</v>
+        <v>44862</v>
       </c>
       <c r="H57" t="n">
-        <v>96.5</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="I57" t="n">
         <v>97.04011146968701</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K57" t="n">
-        <v>6.17</v>
+        <v>2.92</v>
       </c>
       <c r="L57" t="n">
         <v>1.22</v>
@@ -3690,7 +4373,7 @@
         <v>1.39</v>
       </c>
       <c r="N57" t="n">
-        <v>2.45</v>
+        <v>3.47</v>
       </c>
       <c r="O57" t="n">
         <v>-0.68</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>3</v>
+      </c>
+      <c r="U57" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>7.33</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>44951</v>
+        <v>44953</v>
       </c>
       <c r="H58" t="n">
-        <v>120.5</v>
+        <v>115.15</v>
       </c>
       <c r="I58" t="n">
         <v>116.6477105263805</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K58" t="n">
-        <v>20.68</v>
+        <v>15.32</v>
       </c>
       <c r="L58" t="n">
         <v>3.1</v>
@@ -3747,7 +4442,7 @@
         <v>3.65</v>
       </c>
       <c r="N58" t="n">
-        <v>3.33</v>
+        <v>4.44</v>
       </c>
       <c r="O58" t="n">
         <v>3.47</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>4</v>
+      </c>
+      <c r="U58" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>9.75</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>44988</v>
+        <v>44991</v>
       </c>
       <c r="H59" t="n">
-        <v>118.15</v>
+        <v>121.45</v>
       </c>
       <c r="I59" t="n">
         <v>120.0673385672165</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K59" t="n">
-        <v>-2.61</v>
+        <v>-5.47</v>
       </c>
       <c r="L59" t="n">
         <v>7.12</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,22 +4559,22 @@
         <v>7.74</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>44998</v>
+        <v>44999</v>
       </c>
       <c r="H60" t="n">
-        <v>119.65</v>
+        <v>117.05</v>
       </c>
       <c r="I60" t="n">
         <v>117.4264973295499</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K60" t="n">
-        <v>-1.48</v>
+        <v>-3.62</v>
       </c>
       <c r="L60" t="n">
-        <v>2.63</v>
+        <v>3.87</v>
       </c>
       <c r="M60" t="n">
         <v>0.54</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>9.449999999999999</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45022</v>
+        <v>45026</v>
       </c>
       <c r="H61" t="n">
-        <v>118.75</v>
+        <v>124.05</v>
       </c>
       <c r="I61" t="n">
         <v>122.8145968893292</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K61" t="n">
-        <v>-1.45</v>
+        <v>-5.98</v>
       </c>
       <c r="L61" t="n">
-        <v>2.61</v>
+        <v>6.32</v>
       </c>
       <c r="M61" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="N61" t="n">
-        <v>2.15</v>
+        <v>4.46</v>
       </c>
       <c r="O61" t="n">
         <v>-2.17</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>9.140000000000001</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45181</v>
+        <v>45182</v>
       </c>
       <c r="H62" t="n">
-        <v>248.35</v>
+        <v>244.4</v>
       </c>
       <c r="I62" t="n">
         <v>244.6243477496794</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K62" t="n">
-        <v>100.2</v>
+        <v>97.02</v>
       </c>
       <c r="L62" t="n">
         <v>4.43</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>108</v>
+        <v>109</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>6</v>
+      </c>
+      <c r="U62" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="63">
@@ -4011,28 +4766,28 @@
         <v>16.05</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45195</v>
+        <v>45196</v>
       </c>
       <c r="H63" t="n">
-        <v>267.3</v>
+        <v>284.35</v>
       </c>
       <c r="I63" t="n">
         <v>282.3599754904837</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K63" t="n">
-        <v>-9.369999999999999</v>
+        <v>-16.35</v>
       </c>
       <c r="L63" t="n">
-        <v>11.87</v>
+        <v>17</v>
       </c>
       <c r="M63" t="n">
         <v>1.1</v>
       </c>
       <c r="N63" t="n">
-        <v>4.55</v>
+        <v>6.38</v>
       </c>
       <c r="O63" t="n">
         <v>-1.59</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,25 +4835,25 @@
         <v>15.33</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45224</v>
+        <v>45225</v>
       </c>
       <c r="H64" t="n">
-        <v>273.3</v>
+        <v>265.75</v>
       </c>
       <c r="I64" t="n">
         <v>267.9576598092887</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K64" t="n">
-        <v>-3.89</v>
+        <v>-6.54</v>
       </c>
       <c r="L64" t="n">
-        <v>6.03</v>
+        <v>8.76</v>
       </c>
       <c r="M64" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="N64" t="n">
         <v>3.32</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>12.19</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45231</v>
+        <v>45232</v>
       </c>
       <c r="H65" t="n">
-        <v>282.85</v>
+        <v>302.4</v>
       </c>
       <c r="I65" t="n">
         <v>298.1509531632918</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K65" t="n">
-        <v>-6.43</v>
+        <v>-13.79</v>
       </c>
       <c r="L65" t="n">
-        <v>9.84</v>
+        <v>15.67</v>
       </c>
       <c r="M65" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="N65" t="n">
-        <v>3.3</v>
+        <v>6.91</v>
       </c>
       <c r="O65" t="n">
         <v>-2.76</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>14.63</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45331</v>
+        <v>45334</v>
       </c>
       <c r="H66" t="n">
-        <v>482.4</v>
+        <v>453.55</v>
       </c>
       <c r="I66" t="n">
         <v>454.4553329568618</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="K66" t="n">
-        <v>59.52</v>
+        <v>49.98</v>
       </c>
       <c r="L66" t="n">
         <v>5.06</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>4</v>
+      </c>
+      <c r="U66" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="67">
@@ -4239,28 +5042,28 @@
         <v>19.55</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45411</v>
+        <v>45412</v>
       </c>
       <c r="H67" t="n">
-        <v>463</v>
+        <v>507.15</v>
       </c>
       <c r="I67" t="n">
         <v>469.5446949111329</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K67" t="n">
-        <v>-2.08</v>
+        <v>-11.82</v>
       </c>
       <c r="L67" t="n">
-        <v>8.5</v>
+        <v>12.81</v>
       </c>
       <c r="M67" t="n">
         <v>1.65</v>
       </c>
       <c r="N67" t="n">
-        <v>6.44</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="O67" t="n">
         <v>-5.98</v>
@@ -4269,7 +5072,19 @@
         <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>4</v>
+      </c>
+      <c r="U67" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="68">
@@ -4296,28 +5111,28 @@
         <v>14.04</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H68" t="n">
-        <v>604.5</v>
+        <v>452.2</v>
       </c>
       <c r="I68" t="n">
         <v>512.867201161365</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K68" t="n">
-        <v>19.2</v>
+        <v>-10.84</v>
       </c>
       <c r="L68" t="n">
-        <v>8.67</v>
+        <v>12.06</v>
       </c>
       <c r="M68" t="n">
         <v>4.8</v>
       </c>
       <c r="N68" t="n">
-        <v>7.39</v>
+        <v>25.19</v>
       </c>
       <c r="O68" t="n">
         <v>9.539999999999999</v>
@@ -4326,7 +5141,19 @@
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>41.74</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45476</v>
+        <v>45477</v>
       </c>
       <c r="H69" t="n">
-        <v>562.3</v>
+        <v>575.65</v>
       </c>
       <c r="I69" t="n">
         <v>568.1000796362256</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K69" t="n">
-        <v>-24.35</v>
+        <v>-27.3</v>
       </c>
       <c r="L69" t="n">
         <v>31.36</v>
@@ -4383,7 +5210,19 @@
         <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,22 +5249,22 @@
         <v>12.06</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="H70" t="n">
-        <v>579.1</v>
+        <v>565.45</v>
       </c>
       <c r="I70" t="n">
         <v>575.4648779595341</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K70" t="n">
-        <v>0.6</v>
+        <v>-1.77</v>
       </c>
       <c r="L70" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="M70" t="n">
         <v>3.76</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>2</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -4467,19 +5318,19 @@
         <v>17.63</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>45537</v>
+        <v>45538</v>
       </c>
       <c r="H71" t="n">
-        <v>617.15</v>
+        <v>629.4</v>
       </c>
       <c r="I71" t="n">
         <v>628.8959932057728</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K71" t="n">
-        <v>-9.140000000000001</v>
+        <v>-11.31</v>
       </c>
       <c r="L71" t="n">
         <v>12.48</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4524,22 +5387,22 @@
         <v>9.119999999999999</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="H72" t="n">
-        <v>590.05</v>
+        <v>577.15</v>
       </c>
       <c r="I72" t="n">
         <v>583.1252047598491</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K72" t="n">
-        <v>-6.25</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="L72" t="n">
-        <v>7.76</v>
+        <v>8.75</v>
       </c>
       <c r="M72" t="n">
         <v>1.81</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S72" t="b">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>1</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -4581,19 +5456,19 @@
         <v>10.93</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>45631</v>
+        <v>45632</v>
       </c>
       <c r="H73" t="n">
-        <v>545</v>
+        <v>559.1</v>
       </c>
       <c r="I73" t="n">
         <v>557.9727530168331</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K73" t="n">
-        <v>5.57</v>
+        <v>3.13</v>
       </c>
       <c r="L73" t="n">
         <v>3.36</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>4</v>
+      </c>
+      <c r="U73" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="74">
@@ -4638,28 +5525,28 @@
         <v>9.720000000000001</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>45645</v>
+        <v>45646</v>
       </c>
       <c r="H74" t="n">
-        <v>529.1</v>
+        <v>513.25</v>
       </c>
       <c r="I74" t="n">
         <v>526.2428694865458</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K74" t="n">
-        <v>-5.37</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="L74" t="n">
-        <v>7.32</v>
+        <v>8.73</v>
       </c>
       <c r="M74" t="n">
         <v>2.79</v>
       </c>
       <c r="N74" t="n">
-        <v>2.42</v>
+        <v>3</v>
       </c>
       <c r="O74" t="n">
         <v>2.59</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S74" t="b">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>1</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -4695,19 +5594,19 @@
         <v>11.01</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>45733</v>
+        <v>45734</v>
       </c>
       <c r="H75" t="n">
-        <v>412.9</v>
+        <v>421.55</v>
       </c>
       <c r="I75" t="n">
         <v>420.48485511649</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K75" t="n">
-        <v>19.55</v>
+        <v>17.87</v>
       </c>
       <c r="L75" t="n">
         <v>6.13</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>4</v>
+      </c>
+      <c r="U75" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="76">
@@ -4752,25 +5663,25 @@
         <v>11.73</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>45751</v>
+        <v>45754</v>
       </c>
       <c r="H76" t="n">
-        <v>403.4</v>
+        <v>384.35</v>
       </c>
       <c r="I76" t="n">
         <v>402.4461873002475</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K76" t="n">
-        <v>-4.31</v>
+        <v>-8.82</v>
       </c>
       <c r="L76" t="n">
-        <v>4.85</v>
+        <v>13.05</v>
       </c>
       <c r="M76" t="n">
-        <v>1.31</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="N76" t="n">
         <v>5.18</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>2</v>
+      </c>
+      <c r="U76" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -4809,22 +5732,22 @@
         <v>12.09</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>45764</v>
+        <v>45768</v>
       </c>
       <c r="H77" t="n">
-        <v>428.6</v>
+        <v>442.6</v>
       </c>
       <c r="I77" t="n">
         <v>430.817929978225</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K77" t="n">
-        <v>-11.51</v>
+        <v>-15.16</v>
       </c>
       <c r="L77" t="n">
-        <v>12.24</v>
+        <v>15.61</v>
       </c>
       <c r="M77" t="n">
         <v>3.98</v>
@@ -4839,7 +5762,19 @@
         <v>1</v>
       </c>
       <c r="Q77" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S77" t="b">
+        <v>0</v>
+      </c>
+      <c r="T77" t="n">
+        <v>1</v>
+      </c>
+      <c r="U77" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -4866,28 +5801,28 @@
         <v>12.43</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>45784</v>
+        <v>45785</v>
       </c>
       <c r="H78" t="n">
-        <v>410.95</v>
+        <v>392.4</v>
       </c>
       <c r="I78" t="n">
         <v>396.046974211159</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K78" t="n">
-        <v>-7.15</v>
+        <v>-11.34</v>
       </c>
       <c r="L78" t="n">
-        <v>10.55</v>
+        <v>12.11</v>
       </c>
       <c r="M78" t="n">
         <v>1.98</v>
       </c>
       <c r="N78" t="n">
-        <v>4.39</v>
+        <v>4.51</v>
       </c>
       <c r="O78" t="n">
         <v>3.27</v>
@@ -4896,7 +5831,19 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S78" t="b">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>2</v>
+      </c>
+      <c r="U78" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -4923,19 +5870,19 @@
         <v>15.65</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>45910</v>
+        <v>45911</v>
       </c>
       <c r="H79" t="n">
-        <v>370.95</v>
+        <v>374.65</v>
       </c>
       <c r="I79" t="n">
         <v>373.6017362764952</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K79" t="n">
-        <v>5.47</v>
+        <v>4.52</v>
       </c>
       <c r="L79" t="n">
         <v>9.25</v>
@@ -4953,7 +5900,19 @@
         <v>1</v>
       </c>
       <c r="Q79" t="n">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S79" t="b">
+        <v>1</v>
+      </c>
+      <c r="T79" t="n">
+        <v>5</v>
+      </c>
+      <c r="U79" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="80">
@@ -4980,28 +5939,28 @@
         <v>5.54</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="H80" t="n">
-        <v>375.25</v>
+        <v>367.4</v>
       </c>
       <c r="I80" t="n">
         <v>368.6195169031104</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K80" t="n">
-        <v>0.16</v>
+        <v>-1.94</v>
       </c>
       <c r="L80" t="n">
-        <v>0.97</v>
+        <v>2.58</v>
       </c>
       <c r="M80" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="N80" t="n">
-        <v>1.77</v>
+        <v>2.09</v>
       </c>
       <c r="O80" t="n">
         <v>1</v>
@@ -5010,7 +5969,19 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S80" t="b">
+        <v>0</v>
+      </c>
+      <c r="T80" t="n">
+        <v>1</v>
+      </c>
+      <c r="U80" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -5037,19 +6008,19 @@
         <v>6.23</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="H81" t="n">
-        <v>354.2</v>
+        <v>354.75</v>
       </c>
       <c r="I81" t="n">
         <v>354.6552382378317</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K81" t="n">
-        <v>3.59</v>
+        <v>3.44</v>
       </c>
       <c r="L81" t="n">
         <v>6.23</v>
@@ -5067,7 +6038,19 @@
         <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R81" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S81" t="b">
+        <v>1</v>
+      </c>
+      <c r="T81" t="n">
+        <v>4</v>
+      </c>
+      <c r="U81" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="82">
@@ -5094,19 +6077,19 @@
         <v>5.53</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>46041</v>
+        <v>46042</v>
       </c>
       <c r="H82" t="n">
-        <v>370.1</v>
+        <v>358.9</v>
       </c>
       <c r="I82" t="n">
         <v>359.3806069546433</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K82" t="n">
-        <v>4.33</v>
+        <v>1.17</v>
       </c>
       <c r="L82" t="n">
         <v>1.34</v>
@@ -5124,7 +6107,19 @@
         <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R82" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S82" t="b">
+        <v>1</v>
+      </c>
+      <c r="T82" t="n">
+        <v>2</v>
+      </c>
+      <c r="U82" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -5151,19 +6146,19 @@
         <v>9.25</v>
       </c>
       <c r="G83" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="H83" t="n">
-        <v>346.8</v>
+        <v>349.8</v>
       </c>
       <c r="I83" t="n">
         <v>348.7771340715376</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K83" t="n">
-        <v>3.37</v>
+        <v>2.54</v>
       </c>
       <c r="L83" t="n">
         <v>7.69</v>
@@ -5181,7 +6176,19 @@
         <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R83" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S83" t="b">
+        <v>1</v>
+      </c>
+      <c r="T83" t="n">
+        <v>4</v>
+      </c>
+      <c r="U83" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="84">
@@ -5208,19 +6215,19 @@
         <v>10.15</v>
       </c>
       <c r="G84" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="H84" t="n">
-        <v>351.55</v>
+        <v>344.35</v>
       </c>
       <c r="I84" t="n">
         <v>346.1481459511391</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K84" t="n">
-        <v>0.5</v>
+        <v>-1.56</v>
       </c>
       <c r="L84" t="n">
         <v>3.44</v>
@@ -5238,7 +6245,19 @@
         <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R84" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S84" t="b">
+        <v>1</v>
+      </c>
+      <c r="T84" t="n">
+        <v>2</v>
+      </c>
+      <c r="U84" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="85">
@@ -5265,19 +6284,19 @@
         <v>10.25</v>
       </c>
       <c r="G85" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H85" t="n">
-        <v>343.4</v>
+        <v>352.1</v>
       </c>
       <c r="I85" t="n">
         <v>349.2366906708066</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K85" t="n">
-        <v>0.28</v>
+        <v>-2.25</v>
       </c>
       <c r="L85" t="n">
         <v>2.7</v>
@@ -5295,7 +6314,19 @@
         <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R85" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S85" t="b">
+        <v>1</v>
+      </c>
+      <c r="T85" t="n">
+        <v>2</v>
+      </c>
+      <c r="U85" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="86">
@@ -5322,19 +6353,19 @@
         <v>8.539999999999999</v>
       </c>
       <c r="G86" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="H86" t="n">
-        <v>367</v>
+        <v>343.75</v>
       </c>
       <c r="I86" t="n">
         <v>350.1443386838396</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K86" t="n">
-        <v>4.23</v>
+        <v>-2.37</v>
       </c>
       <c r="L86" t="n">
         <v>4.66</v>
@@ -5343,7 +6374,7 @@
         <v>1.13</v>
       </c>
       <c r="N86" t="n">
-        <v>3.43</v>
+        <v>6.34</v>
       </c>
       <c r="O86" t="n">
         <v>2.53</v>
@@ -5352,7 +6383,19 @@
         <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R86" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S86" t="b">
+        <v>1</v>
+      </c>
+      <c r="T86" t="n">
+        <v>3</v>
+      </c>
+      <c r="U86" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="87">
@@ -5403,6 +6446,14 @@
       <c r="Q87" t="n">
         <v>55</v>
       </c>
+      <c r="R87" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S87" t="b">
+        <v>1</v>
+      </c>
+      <c r="T87" t="inlineStr"/>
+      <c r="U87" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10361,7 +11412,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>48.2</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="6">
@@ -10371,7 +11422,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7">
@@ -10381,7 +11432,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="8">
@@ -10391,7 +11442,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -10401,7 +11452,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10">
@@ -10411,7 +11462,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="11">
@@ -10451,7 +11502,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.56</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -10461,7 +11512,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6.35</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="16">
@@ -10471,7 +11522,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.71</v>
+        <v>-2.52</v>
       </c>
     </row>
     <row r="17">
@@ -10481,7 +11532,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>100.2</v>
+        <v>97.02</v>
       </c>
     </row>
     <row r="18">
@@ -10491,7 +11542,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>43.5</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="19">
@@ -10501,7 +11552,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.53</v>
+        <v>7.81</v>
       </c>
     </row>
     <row r="20">
@@ -10511,7 +11562,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.74</v>
+        <v>6.86</v>
       </c>
     </row>
     <row r="21">
@@ -10531,7 +11582,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23">
@@ -10541,7 +11592,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24">
@@ -10551,7 +11602,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.04</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="25">
@@ -10561,7 +11612,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>7</v>
+        <v>8.789999999999999</v>
       </c>
     </row>
     <row r="26">
@@ -10571,7 +11622,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.62</v>
+        <v>5.31</v>
       </c>
     </row>
     <row r="27">
@@ -10581,7 +11632,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>12.44</v>
+        <v>25.19</v>
       </c>
     </row>
     <row r="28">
@@ -10591,7 +11642,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
     </row>
     <row r="29">
